--- a/skills/build-gateway-routing-config/assets/网关路由配置表空白模板.xlsx
+++ b/skills/build-gateway-routing-config/assets/网关路由配置表空白模板.xlsx
@@ -10761,7 +10761,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>整帧按使能字段写入；CAN 诊断固定 true。</t>
+          <t>整帧列留空；普通路由和 CanTp 诊断路由均不写入该参数。未参与路由的 Tx 保持原样。</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
